--- a/-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
+++ b/-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92D95FB-6493-48A3-8CA9-E982C11F35C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F326A579-5793-4CBA-892C-479BE1CECAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="1440" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="18000" windowHeight="9270" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -424,13 +427,13 @@
     </row>
     <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -447,13 +450,13 @@
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -470,13 +473,13 @@
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -493,25 +496,25 @@
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
